--- a/backend/excel-templates/test-data/master_student_users_test_data.xlsx
+++ b/backend/excel-templates/test-data/master_student_users_test_data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Students" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,22 +424,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>anup.baral@pcampus.edu.np</v>
+        <v>mstudent1@pcampus.edu.np</v>
       </c>
       <c r="B2" t="str">
-        <v>pass123</v>
+        <v>subesh</v>
       </c>
       <c r="C2" t="str">
-        <v>Anup</v>
+        <v>MStudent</v>
       </c>
       <c r="D2" t="str">
-        <v>Baral</v>
+        <v>1</v>
       </c>
       <c r="E2" t="str">
-        <v>080MSCS01</v>
+        <v>79MSICE01</v>
       </c>
       <c r="F2" t="str">
-        <v>MSCS</v>
+        <v>MSICE</v>
       </c>
       <c r="G2" t="str">
         <v>MASTER</v>
@@ -447,19 +447,19 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>bina.thapa@pcampus.edu.np</v>
+        <v>mstudent2@pcampus.edu.np</v>
       </c>
       <c r="B3" t="str">
-        <v>pass123</v>
+        <v>subesh</v>
       </c>
       <c r="C3" t="str">
-        <v>Bina</v>
+        <v>MStudent</v>
       </c>
       <c r="D3" t="str">
-        <v>Thapa</v>
+        <v>2</v>
       </c>
       <c r="E3" t="str">
-        <v>080MSDSA01</v>
+        <v>79MSDSA02</v>
       </c>
       <c r="F3" t="str">
         <v>MSDSA</v>
@@ -470,30 +470,421 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>krishna.sharma@pcampus.edu.np</v>
+        <v>mstudent3@pcampus.edu.np</v>
       </c>
       <c r="B4" t="str">
-        <v>pass123</v>
+        <v>subesh</v>
       </c>
       <c r="C4" t="str">
-        <v>Krishna</v>
+        <v>MStudent</v>
       </c>
       <c r="D4" t="str">
-        <v>Sharma</v>
+        <v>3</v>
       </c>
       <c r="E4" t="str">
-        <v>080MSNCS01</v>
+        <v>79MSCSKE03</v>
       </c>
       <c r="F4" t="str">
+        <v>MSCSKE</v>
+      </c>
+      <c r="G4" t="str">
+        <v>MASTER</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>mstudent4@pcampus.edu.np</v>
+      </c>
+      <c r="B5" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C5" t="str">
+        <v>MStudent</v>
+      </c>
+      <c r="D5" t="str">
+        <v>4</v>
+      </c>
+      <c r="E5" t="str">
+        <v>79MSNCS04</v>
+      </c>
+      <c r="F5" t="str">
         <v>MSNCS</v>
       </c>
-      <c r="G4" t="str">
+      <c r="G5" t="str">
+        <v>MASTER</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>mstudent5@pcampus.edu.np</v>
+      </c>
+      <c r="B6" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C6" t="str">
+        <v>MStudent</v>
+      </c>
+      <c r="D6" t="str">
+        <v>5</v>
+      </c>
+      <c r="E6" t="str">
+        <v>79MSICE05</v>
+      </c>
+      <c r="F6" t="str">
+        <v>MSICE</v>
+      </c>
+      <c r="G6" t="str">
+        <v>MASTER</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>mstudent6@pcampus.edu.np</v>
+      </c>
+      <c r="B7" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C7" t="str">
+        <v>MStudent</v>
+      </c>
+      <c r="D7" t="str">
+        <v>6</v>
+      </c>
+      <c r="E7" t="str">
+        <v>79MSDSA06</v>
+      </c>
+      <c r="F7" t="str">
+        <v>MSDSA</v>
+      </c>
+      <c r="G7" t="str">
+        <v>MASTER</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>mstudent7@pcampus.edu.np</v>
+      </c>
+      <c r="B8" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C8" t="str">
+        <v>MStudent</v>
+      </c>
+      <c r="D8" t="str">
+        <v>7</v>
+      </c>
+      <c r="E8" t="str">
+        <v>79MSCSKE07</v>
+      </c>
+      <c r="F8" t="str">
+        <v>MSCSKE</v>
+      </c>
+      <c r="G8" t="str">
+        <v>MASTER</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>mstudent8@pcampus.edu.np</v>
+      </c>
+      <c r="B9" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C9" t="str">
+        <v>MStudent</v>
+      </c>
+      <c r="D9" t="str">
+        <v>8</v>
+      </c>
+      <c r="E9" t="str">
+        <v>80MSNCS08</v>
+      </c>
+      <c r="F9" t="str">
+        <v>MSNCS</v>
+      </c>
+      <c r="G9" t="str">
+        <v>MASTER</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>mstudent9@pcampus.edu.np</v>
+      </c>
+      <c r="B10" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C10" t="str">
+        <v>MStudent</v>
+      </c>
+      <c r="D10" t="str">
+        <v>9</v>
+      </c>
+      <c r="E10" t="str">
+        <v>80MSICE09</v>
+      </c>
+      <c r="F10" t="str">
+        <v>MSICE</v>
+      </c>
+      <c r="G10" t="str">
+        <v>MASTER</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>mstudent10@pcampus.edu.np</v>
+      </c>
+      <c r="B11" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C11" t="str">
+        <v>MStudent</v>
+      </c>
+      <c r="D11" t="str">
+        <v>10</v>
+      </c>
+      <c r="E11" t="str">
+        <v>80MSDSA10</v>
+      </c>
+      <c r="F11" t="str">
+        <v>MSDSA</v>
+      </c>
+      <c r="G11" t="str">
+        <v>MASTER</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>mstudent11@pcampus.edu.np</v>
+      </c>
+      <c r="B12" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C12" t="str">
+        <v>MStudent</v>
+      </c>
+      <c r="D12" t="str">
+        <v>11</v>
+      </c>
+      <c r="E12" t="str">
+        <v>80MSCSKE11</v>
+      </c>
+      <c r="F12" t="str">
+        <v>MSCSKE</v>
+      </c>
+      <c r="G12" t="str">
+        <v>MASTER</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>mstudent12@pcampus.edu.np</v>
+      </c>
+      <c r="B13" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C13" t="str">
+        <v>MStudent</v>
+      </c>
+      <c r="D13" t="str">
+        <v>12</v>
+      </c>
+      <c r="E13" t="str">
+        <v>80MSNCS12</v>
+      </c>
+      <c r="F13" t="str">
+        <v>MSNCS</v>
+      </c>
+      <c r="G13" t="str">
+        <v>MASTER</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>mstudent13@pcampus.edu.np</v>
+      </c>
+      <c r="B14" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C14" t="str">
+        <v>MStudent</v>
+      </c>
+      <c r="D14" t="str">
+        <v>13</v>
+      </c>
+      <c r="E14" t="str">
+        <v>80MSICE13</v>
+      </c>
+      <c r="F14" t="str">
+        <v>MSICE</v>
+      </c>
+      <c r="G14" t="str">
+        <v>MASTER</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>mstudent14@pcampus.edu.np</v>
+      </c>
+      <c r="B15" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C15" t="str">
+        <v>MStudent</v>
+      </c>
+      <c r="D15" t="str">
+        <v>14</v>
+      </c>
+      <c r="E15" t="str">
+        <v>80MSDSA14</v>
+      </c>
+      <c r="F15" t="str">
+        <v>MSDSA</v>
+      </c>
+      <c r="G15" t="str">
+        <v>MASTER</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>mstudent15@pcampus.edu.np</v>
+      </c>
+      <c r="B16" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C16" t="str">
+        <v>MStudent</v>
+      </c>
+      <c r="D16" t="str">
+        <v>15</v>
+      </c>
+      <c r="E16" t="str">
+        <v>80MSCSKE15</v>
+      </c>
+      <c r="F16" t="str">
+        <v>MSCSKE</v>
+      </c>
+      <c r="G16" t="str">
+        <v>MASTER</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>mstudent16@pcampus.edu.np</v>
+      </c>
+      <c r="B17" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C17" t="str">
+        <v>MStudent</v>
+      </c>
+      <c r="D17" t="str">
+        <v>16</v>
+      </c>
+      <c r="E17" t="str">
+        <v>81MSNCS16</v>
+      </c>
+      <c r="F17" t="str">
+        <v>MSNCS</v>
+      </c>
+      <c r="G17" t="str">
+        <v>MASTER</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>mstudent17@pcampus.edu.np</v>
+      </c>
+      <c r="B18" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C18" t="str">
+        <v>MStudent</v>
+      </c>
+      <c r="D18" t="str">
+        <v>17</v>
+      </c>
+      <c r="E18" t="str">
+        <v>81MSICE17</v>
+      </c>
+      <c r="F18" t="str">
+        <v>MSICE</v>
+      </c>
+      <c r="G18" t="str">
+        <v>MASTER</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>mstudent18@pcampus.edu.np</v>
+      </c>
+      <c r="B19" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C19" t="str">
+        <v>MStudent</v>
+      </c>
+      <c r="D19" t="str">
+        <v>18</v>
+      </c>
+      <c r="E19" t="str">
+        <v>81MSDSA18</v>
+      </c>
+      <c r="F19" t="str">
+        <v>MSDSA</v>
+      </c>
+      <c r="G19" t="str">
+        <v>MASTER</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>mstudent19@pcampus.edu.np</v>
+      </c>
+      <c r="B20" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C20" t="str">
+        <v>MStudent</v>
+      </c>
+      <c r="D20" t="str">
+        <v>19</v>
+      </c>
+      <c r="E20" t="str">
+        <v>81MSCSKE19</v>
+      </c>
+      <c r="F20" t="str">
+        <v>MSCSKE</v>
+      </c>
+      <c r="G20" t="str">
+        <v>MASTER</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>mstudent20@pcampus.edu.np</v>
+      </c>
+      <c r="B21" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C21" t="str">
+        <v>MStudent</v>
+      </c>
+      <c r="D21" t="str">
+        <v>20</v>
+      </c>
+      <c r="E21" t="str">
+        <v>81MSNCS20</v>
+      </c>
+      <c r="F21" t="str">
+        <v>MSNCS</v>
+      </c>
+      <c r="G21" t="str">
         <v>MASTER</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G21"/>
   </ignoredErrors>
 </worksheet>
 </file>